--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Churchill River Mineral Sands</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>013F/08/Fe 001</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>41</v>
       </c>
       <c r="V3" t="n">
-        <v>53.29106</v>
+        <v>48.69485</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.2677</v>
+        <v>-58.68177</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>Churchill River Mineral Sands</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>013F/08/Fe 001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>41</v>
       </c>
       <c r="V4" t="n">
-        <v>48.69485</v>
+        <v>53.29106</v>
       </c>
       <c r="W4" t="n">
-        <v>-58.68177</v>
+        <v>-60.2677</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>47.4063</v>
+        <v>47.4438</v>
       </c>
       <c r="W7" t="n">
-        <v>-52.70699</v>
+        <v>-54.4169</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1057,14 +1057,14 @@
         <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>47.4438</v>
+        <v>47.4063</v>
       </c>
       <c r="W8" t="n">
-        <v>-54.4169</v>
+        <v>-52.70699</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1408,23 +1408,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U13" t="n">
         <v>30</v>
       </c>
       <c r="V13" t="n">
-        <v>53.40462</v>
+        <v>48.56074</v>
       </c>
       <c r="W13" t="n">
-        <v>-65.08734</v>
+        <v>-58.8161</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1552,23 +1552,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>30</v>
       </c>
       <c r="V15" t="n">
-        <v>48.56074</v>
+        <v>53.40462</v>
       </c>
       <c r="W15" t="n">
-        <v>-58.8161</v>
+        <v>-65.08734</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1768,23 +1768,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T18" t="n">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="U18" t="n">
         <v>29</v>
       </c>
       <c r="V18" t="n">
-        <v>50.27283</v>
+        <v>50.31118</v>
       </c>
       <c r="W18" t="n">
-        <v>-57.46448</v>
+        <v>-57.43009</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1840,23 +1840,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T19" t="n">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="U19" t="n">
         <v>29</v>
       </c>
       <c r="V19" t="n">
-        <v>50.31118</v>
+        <v>50.27283</v>
       </c>
       <c r="W19" t="n">
-        <v>-57.43009</v>
+        <v>-57.46448</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Workington</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>002C/03/Fe 001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>26</v>
       </c>
       <c r="V20" t="n">
-        <v>49.50376</v>
+        <v>48.00096</v>
       </c>
       <c r="W20" t="n">
-        <v>-55.21553</v>
+        <v>-53.01864</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -2010,24 +2010,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Workington</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>002C/03/Fe 001</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>26</v>
       </c>
       <c r="V22" t="n">
-        <v>48.00096</v>
+        <v>49.50376</v>
       </c>
       <c r="W22" t="n">
-        <v>-53.01864</v>
+        <v>-55.21553</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>Churchill River Mineral Sands</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>013F/08/Fe 001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>41</v>
       </c>
       <c r="V3" t="n">
-        <v>48.69485</v>
+        <v>53.29106</v>
       </c>
       <c r="W3" t="n">
-        <v>-58.68177</v>
+        <v>-60.2677</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Churchill River Mineral Sands</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>013F/08/Fe 001</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>41</v>
       </c>
       <c r="V4" t="n">
-        <v>53.29106</v>
+        <v>48.69485</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.2677</v>
+        <v>-58.68177</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>47.4438</v>
+        <v>47.4063</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.4169</v>
+        <v>-52.70699</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1057,14 +1057,14 @@
         <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>47.4063</v>
+        <v>47.4438</v>
       </c>
       <c r="W8" t="n">
-        <v>-52.70699</v>
+        <v>-54.4169</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1408,23 +1408,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>30</v>
       </c>
       <c r="V13" t="n">
-        <v>48.56074</v>
+        <v>53.40462</v>
       </c>
       <c r="W13" t="n">
-        <v>-58.8161</v>
+        <v>-65.08734</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1552,23 +1552,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U15" t="n">
         <v>30</v>
       </c>
       <c r="V15" t="n">
-        <v>53.40462</v>
+        <v>48.56074</v>
       </c>
       <c r="W15" t="n">
-        <v>-65.08734</v>
+        <v>-58.8161</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1768,23 +1768,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="U18" t="n">
         <v>29</v>
       </c>
       <c r="V18" t="n">
-        <v>50.31118</v>
+        <v>50.27283</v>
       </c>
       <c r="W18" t="n">
-        <v>-57.43009</v>
+        <v>-57.46448</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1840,23 +1840,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>250</v>
+        <v>175</v>
       </c>
       <c r="U19" t="n">
         <v>29</v>
       </c>
       <c r="V19" t="n">
-        <v>50.27283</v>
+        <v>50.31118</v>
       </c>
       <c r="W19" t="n">
-        <v>-57.46448</v>
+        <v>-57.43009</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Workington</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>002C/03/Fe 001</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>26</v>
       </c>
       <c r="V20" t="n">
-        <v>48.00096</v>
+        <v>49.50376</v>
       </c>
       <c r="W20" t="n">
-        <v>-53.01864</v>
+        <v>-55.21553</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -2010,24 +2010,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Workington</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>002C/03/Fe 001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>26</v>
       </c>
       <c r="V22" t="n">
-        <v>49.50376</v>
+        <v>48.00096</v>
       </c>
       <c r="W22" t="n">
-        <v>-55.21553</v>
+        <v>-53.01864</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -1768,10 +1768,10 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="U18" t="n">
         <v>29</v>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -858,29 +858,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sheep Brook</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>012B/08/Gyp001</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Developed Prospect</t>
+          <t>Past Producer</t>
         </is>
       </c>
       <c r="I6" t="b">
@@ -904,23 +904,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>48.39536</v>
+        <v>47.4438</v>
       </c>
       <c r="W6" t="n">
-        <v>-58.42046</v>
+        <v>-54.4169</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F08%2FGyp001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>47.4438</v>
+        <v>47.4063</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.4169</v>
+        <v>-52.70699</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1002,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Lower Drill Brook Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>012B/09/Fe 003</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1048,23 +1048,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="U8" t="n">
         <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>47.4063</v>
+        <v>48.5353</v>
       </c>
       <c r="W8" t="n">
-        <v>-52.70699</v>
+        <v>-58.48804</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lower Drill Brook Mine</t>
+          <t>Goose Arm Brook</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>012B/09/Fe 003</t>
+          <t>012H/04/Pb 001</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Titanium, Vanadium, Iron</t>
+          <t>Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1120,23 +1120,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>48.5353</v>
+        <v>49.19579</v>
       </c>
       <c r="W9" t="n">
-        <v>-58.48804</v>
+        <v>-57.84974</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F09%2FFe%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Goose Arm Brook</t>
+          <t>Albert Lake Quarry-South</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>012H/04/Pb 001</t>
+          <t>023B/15/Dol001</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Zinc, Lead</t>
+          <t>Copper, Dolomite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>35</v>
       </c>
       <c r="V10" t="n">
-        <v>49.19579</v>
+        <v>52.961</v>
       </c>
       <c r="W10" t="n">
-        <v>-57.84974</v>
+        <v>-66.81446</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012H%2F04%2FPb%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1218,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Albert Lake Quarry-South</t>
+          <t>Ossokmanuan Lake North Quarry</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>023B/15/Dol001</t>
+          <t>023H/07/Stn001</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Dolomite</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1264,23 +1264,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V11" t="n">
-        <v>52.961</v>
+        <v>53.469</v>
       </c>
       <c r="W11" t="n">
-        <v>-66.81446</v>
+        <v>-64.91218000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023B%2F15%2FDol001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake North Quarry</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>023H/07/Stn001</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1336,23 +1336,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>275</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>53.469</v>
+        <v>48.56074</v>
       </c>
       <c r="W12" t="n">
-        <v>-64.91218000000001</v>
+        <v>-58.8161</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F07%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Trinity Brick Quarry</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>002C/04/Shl001</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Shale</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1408,23 +1408,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>30</v>
       </c>
       <c r="V13" t="n">
-        <v>48.56074</v>
+        <v>48.20248</v>
       </c>
       <c r="W13" t="n">
-        <v>-58.8161</v>
+        <v>-53.94461</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F04%2FShl001</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Trinity Brick Quarry</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>002C/04/Shl001</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Shale</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>30</v>
       </c>
       <c r="V14" t="n">
-        <v>48.20248</v>
+        <v>53.40462</v>
       </c>
       <c r="W14" t="n">
-        <v>-53.94461</v>
+        <v>-65.08734</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F04%2FShl001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>South Stephenville Pond</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>012B/10/Stn001</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Anorthosite</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1552,23 +1552,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
         <v>30</v>
       </c>
       <c r="V15" t="n">
-        <v>53.40462</v>
+        <v>48.50411</v>
       </c>
       <c r="W15" t="n">
-        <v>-65.08734</v>
+        <v>-58.53451</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
         </is>
       </c>
     </row>
@@ -1578,12 +1578,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>South Stephenville Pond</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>012B/10/Stn001</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anorthosite</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="U16" t="n">
         <v>30</v>
       </c>
       <c r="V16" t="n">
-        <v>48.50411</v>
+        <v>48.30663</v>
       </c>
       <c r="W16" t="n">
-        <v>-58.53451</v>
+        <v>-58.68165</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1702,17 +1702,17 @@
         <v>150</v>
       </c>
       <c r="U17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V17" t="n">
-        <v>48.30663</v>
+        <v>50.31118</v>
       </c>
       <c r="W17" t="n">
-        <v>-58.68165</v>
+        <v>-57.43009</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1768,23 +1768,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U18" t="n">
         <v>29</v>
       </c>
       <c r="V18" t="n">
-        <v>50.31118</v>
+        <v>50.27283</v>
       </c>
       <c r="W18" t="n">
-        <v>-57.43009</v>
+        <v>-57.46448</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Workington</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>002C/03/Fe 001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1840,23 +1840,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="V19" t="n">
-        <v>50.27283</v>
+        <v>48.00096</v>
       </c>
       <c r="W19" t="n">
-        <v>-57.46448</v>
+        <v>-53.01864</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Workington</t>
+          <t>Brigus (South Point)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>002C/03/Fe 001</t>
+          <t>001N/11/Mn 001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>26</v>
       </c>
       <c r="V20" t="n">
-        <v>48.00096</v>
+        <v>47.53392</v>
       </c>
       <c r="W20" t="n">
-        <v>-53.01864</v>
+        <v>-53.18293</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
         </is>
       </c>
     </row>
@@ -1938,12 +1938,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Brigus (South Point)</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>001N/11/Mn 001</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,84 +1993,12 @@
         <v>26</v>
       </c>
       <c r="V21" t="n">
-        <v>47.53392</v>
+        <v>49.50376</v>
       </c>
       <c r="W21" t="n">
-        <v>-53.18293</v>
+        <v>-55.21553</v>
       </c>
       <c r="X21" t="inlineStr">
-        <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Cook Iron Mine</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>002E/11/Fe 001</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Manganese</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Manganese, Iron</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I22" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" t="b">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="n">
-        <v>13</v>
-      </c>
-      <c r="T22" t="n">
-        <v>325</v>
-      </c>
-      <c r="U22" t="n">
-        <v>26</v>
-      </c>
-      <c r="V22" t="n">
-        <v>49.50376</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-55.21553</v>
-      </c>
-      <c r="X22" t="inlineStr">
         <is>
           <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>Churchill River Mineral Sands</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>013F/08/Fe 001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>41</v>
       </c>
       <c r="V3" t="n">
-        <v>48.69485</v>
+        <v>53.29106</v>
       </c>
       <c r="W3" t="n">
-        <v>-58.68177</v>
+        <v>-60.2677</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Churchill River Mineral Sands</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>013F/08/Fe 001</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>41</v>
       </c>
       <c r="V4" t="n">
-        <v>53.29106</v>
+        <v>48.69485</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.2677</v>
+        <v>-58.68177</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>47.4438</v>
+        <v>47.4063</v>
       </c>
       <c r="W6" t="n">
-        <v>-54.4169</v>
+        <v>-52.70699</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>47.4063</v>
+        <v>47.4438</v>
       </c>
       <c r="W7" t="n">
-        <v>-52.70699</v>
+        <v>-54.4169</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1336,23 +1336,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>48.56074</v>
+        <v>53.40462</v>
       </c>
       <c r="W12" t="n">
-        <v>-58.8161</v>
+        <v>-65.08734</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
       </c>
       <c r="V14" t="n">
-        <v>53.40462</v>
+        <v>48.56074</v>
       </c>
       <c r="W14" t="n">
-        <v>-65.08734</v>
+        <v>-58.8161</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1696,23 +1696,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U17" t="n">
         <v>29</v>
       </c>
       <c r="V17" t="n">
-        <v>50.31118</v>
+        <v>50.27283</v>
       </c>
       <c r="W17" t="n">
-        <v>-57.43009</v>
+        <v>-57.46448</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1768,23 +1768,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="U18" t="n">
         <v>29</v>
       </c>
       <c r="V18" t="n">
-        <v>50.27283</v>
+        <v>50.31118</v>
       </c>
       <c r="W18" t="n">
-        <v>-57.46448</v>
+        <v>-57.43009</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Workington</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>002C/03/Fe 001</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>26</v>
       </c>
       <c r="V19" t="n">
-        <v>48.00096</v>
+        <v>49.50376</v>
       </c>
       <c r="W19" t="n">
-        <v>-53.01864</v>
+        <v>-55.21553</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Workington</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>002C/03/Fe 001</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,14 +1993,14 @@
         <v>26</v>
       </c>
       <c r="V21" t="n">
-        <v>49.50376</v>
+        <v>48.00096</v>
       </c>
       <c r="W21" t="n">
-        <v>-55.21553</v>
+        <v>-53.01864</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Churchill River Mineral Sands</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>013F/08/Fe 001</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>41</v>
       </c>
       <c r="V3" t="n">
-        <v>53.29106</v>
+        <v>48.69485</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.2677</v>
+        <v>-58.68177</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>Churchill River Mineral Sands</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>013F/08/Fe 001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>41</v>
       </c>
       <c r="V4" t="n">
-        <v>48.69485</v>
+        <v>53.29106</v>
       </c>
       <c r="W4" t="n">
-        <v>-58.68177</v>
+        <v>-60.2677</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>47.4063</v>
+        <v>47.4438</v>
       </c>
       <c r="W6" t="n">
-        <v>-52.70699</v>
+        <v>-54.4169</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>47.4438</v>
+        <v>47.4063</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.4169</v>
+        <v>-52.70699</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1336,23 +1336,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>53.40462</v>
+        <v>48.56074</v>
       </c>
       <c r="W12" t="n">
-        <v>-65.08734</v>
+        <v>-58.8161</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
       </c>
       <c r="V14" t="n">
-        <v>48.56074</v>
+        <v>53.40462</v>
       </c>
       <c r="W14" t="n">
-        <v>-58.8161</v>
+        <v>-65.08734</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1696,23 +1696,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="U17" t="n">
         <v>29</v>
       </c>
       <c r="V17" t="n">
-        <v>50.27283</v>
+        <v>50.31118</v>
       </c>
       <c r="W17" t="n">
-        <v>-57.46448</v>
+        <v>-57.43009</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1768,23 +1768,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U18" t="n">
         <v>29</v>
       </c>
       <c r="V18" t="n">
-        <v>50.31118</v>
+        <v>50.27283</v>
       </c>
       <c r="W18" t="n">
-        <v>-57.43009</v>
+        <v>-57.46448</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Workington</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>002C/03/Fe 001</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>26</v>
       </c>
       <c r="V19" t="n">
-        <v>49.50376</v>
+        <v>48.00096</v>
       </c>
       <c r="W19" t="n">
-        <v>-55.21553</v>
+        <v>-53.01864</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Workington</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>002C/03/Fe 001</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,14 +1993,14 @@
         <v>26</v>
       </c>
       <c r="V21" t="n">
-        <v>48.00096</v>
+        <v>49.50376</v>
       </c>
       <c r="W21" t="n">
-        <v>-53.01864</v>
+        <v>-55.21553</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Churchill River Mineral Sands</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>013F/08/Fe 001</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>41</v>
       </c>
       <c r="V3" t="n">
-        <v>53.29106</v>
+        <v>48.69485</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.2677</v>
+        <v>-58.68177</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>Churchill River Mineral Sands</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>013F/08/Fe 001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>41</v>
       </c>
       <c r="V4" t="n">
-        <v>48.69485</v>
+        <v>53.29106</v>
       </c>
       <c r="W4" t="n">
-        <v>-58.68177</v>
+        <v>-60.2677</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>47.4063</v>
+        <v>47.4438</v>
       </c>
       <c r="W6" t="n">
-        <v>-52.70699</v>
+        <v>-54.4169</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>47.4438</v>
+        <v>47.4063</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.4169</v>
+        <v>-52.70699</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1336,23 +1336,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>53.40462</v>
+        <v>48.56074</v>
       </c>
       <c r="W12" t="n">
-        <v>-65.08734</v>
+        <v>-58.8161</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
       </c>
       <c r="V14" t="n">
-        <v>48.56074</v>
+        <v>53.40462</v>
       </c>
       <c r="W14" t="n">
-        <v>-58.8161</v>
+        <v>-65.08734</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1696,23 +1696,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>250</v>
+        <v>125</v>
       </c>
       <c r="U17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="V17" t="n">
-        <v>50.27283</v>
+        <v>49.45488</v>
       </c>
       <c r="W17" t="n">
-        <v>-57.46448</v>
+        <v>-55.49811</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1840,23 +1840,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T19" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U19" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="V19" t="n">
-        <v>49.50376</v>
+        <v>50.27283</v>
       </c>
       <c r="W19" t="n">
-        <v>-55.21553</v>
+        <v>-57.46448</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Brigus (South Point)</t>
+          <t>Workington</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>001N/11/Mn 001</t>
+          <t>002C/03/Fe 001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>26</v>
       </c>
       <c r="V20" t="n">
-        <v>47.53392</v>
+        <v>48.00096</v>
       </c>
       <c r="W20" t="n">
-        <v>-53.18293</v>
+        <v>-53.01864</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Workington</t>
+          <t>Brigus (South Point)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>002C/03/Fe 001</t>
+          <t>001N/11/Mn 001</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,14 +1993,86 @@
         <v>26</v>
       </c>
       <c r="V21" t="n">
-        <v>48.00096</v>
+        <v>47.53392</v>
       </c>
       <c r="W21" t="n">
-        <v>-53.01864</v>
+        <v>-53.18293</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F11%2FMn%20001</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cook Iron Mine</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>002E/11/Fe 001</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Manganese</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Manganese, Iron</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Past Producer</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>325</v>
+      </c>
+      <c r="U22" t="n">
+        <v>26</v>
+      </c>
+      <c r="V22" t="n">
+        <v>49.50376</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-55.21553</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>Churchill River Mineral Sands</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>013F/08/Fe 001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>41</v>
       </c>
       <c r="V3" t="n">
-        <v>48.69485</v>
+        <v>53.29106</v>
       </c>
       <c r="W3" t="n">
-        <v>-58.68177</v>
+        <v>-60.2677</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Churchill River Mineral Sands</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>013F/08/Fe 001</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>41</v>
       </c>
       <c r="V4" t="n">
-        <v>53.29106</v>
+        <v>48.69485</v>
       </c>
       <c r="W4" t="n">
-        <v>-60.2677</v>
+        <v>-58.68177</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>47.4438</v>
+        <v>47.4063</v>
       </c>
       <c r="W6" t="n">
-        <v>-54.4169</v>
+        <v>-52.70699</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>47.4063</v>
+        <v>47.4438</v>
       </c>
       <c r="W7" t="n">
-        <v>-52.70699</v>
+        <v>-54.4169</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1336,23 +1336,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>48.56074</v>
+        <v>53.40462</v>
       </c>
       <c r="W12" t="n">
-        <v>-58.8161</v>
+        <v>-65.08734</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
       </c>
       <c r="V14" t="n">
-        <v>53.40462</v>
+        <v>48.56074</v>
       </c>
       <c r="W14" t="n">
-        <v>-65.08734</v>
+        <v>-58.8161</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T16" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="U16" t="n">
         <v>30</v>
       </c>
       <c r="V16" t="n">
-        <v>48.30663</v>
+        <v>49.45488</v>
       </c>
       <c r="W16" t="n">
-        <v>-58.68165</v>
+        <v>-55.49811</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lockport Mine</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>002E/06/Cu 003</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1696,23 +1696,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T17" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U17" t="n">
         <v>30</v>
       </c>
       <c r="V17" t="n">
-        <v>49.45488</v>
+        <v>48.30663</v>
       </c>
       <c r="W17" t="n">
-        <v>-55.49811</v>
+        <v>-58.68165</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1768,23 +1768,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U18" t="n">
         <v>29</v>
       </c>
       <c r="V18" t="n">
-        <v>50.31118</v>
+        <v>50.27283</v>
       </c>
       <c r="W18" t="n">
-        <v>-57.43009</v>
+        <v>-57.46448</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1840,23 +1840,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T19" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="U19" t="n">
         <v>29</v>
       </c>
       <c r="V19" t="n">
-        <v>50.27283</v>
+        <v>50.31118</v>
       </c>
       <c r="W19" t="n">
-        <v>-57.46448</v>
+        <v>-57.43009</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Workington</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>002C/03/Fe 001</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>26</v>
       </c>
       <c r="V20" t="n">
-        <v>48.00096</v>
+        <v>49.50376</v>
       </c>
       <c r="W20" t="n">
-        <v>-53.01864</v>
+        <v>-55.21553</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -2010,24 +2010,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Workington</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>002C/03/Fe 001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>26</v>
       </c>
       <c r="V22" t="n">
-        <v>49.50376</v>
+        <v>48.00096</v>
       </c>
       <c r="W22" t="n">
-        <v>-55.21553</v>
+        <v>-53.01864</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
         </is>
       </c>
     </row>

--- a/site/nl_leads.xlsx
+++ b/site/nl_leads.xlsx
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Churchill River Mineral Sands</t>
+          <t>Fox Island River Area</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>013F/08/Fe 001</t>
+          <t>012B/10/Cr 001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Titanium, Iron</t>
+          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>41</v>
       </c>
       <c r="V3" t="n">
-        <v>53.29106</v>
+        <v>48.69485</v>
       </c>
       <c r="W3" t="n">
-        <v>-60.2677</v>
+        <v>-58.68177</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fox Island River Area</t>
+          <t>Churchill River Mineral Sands</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>012B/10/Cr 001</t>
+          <t>013F/08/Fe 001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Titanium, Garnet, Iron, Olivine, Chromium</t>
+          <t>Titanium, Iron</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>41</v>
       </c>
       <c r="V4" t="n">
-        <v>48.69485</v>
+        <v>53.29106</v>
       </c>
       <c r="W4" t="n">
-        <v>-58.68177</v>
+        <v>-60.2677</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FCr%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=013F%2F08%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Shoal Bay</t>
+          <t>Rocky Cove</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>001N/07/Cu 004</t>
+          <t>001M/08/Cu 001</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>47.4063</v>
+        <v>47.4438</v>
       </c>
       <c r="W6" t="n">
-        <v>-52.70699</v>
+        <v>-54.4169</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Rocky Cove</t>
+          <t>Shoal Bay</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>001M/08/Cu 001</t>
+          <t>001N/07/Cu 004</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>47.4438</v>
+        <v>47.4063</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.4169</v>
+        <v>-52.70699</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001M%2F08%2FCu%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=001N%2F07%2FCu%20004</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ossokmanuan Lake South Quarry</t>
+          <t>Ronan Deposit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>023H/06/Stn001</t>
+          <t>012B/10/Ba 003</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gabbro</t>
+          <t>Strontium, Barium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1336,23 +1336,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>30</v>
       </c>
       <c r="V12" t="n">
-        <v>53.40462</v>
+        <v>48.56074</v>
       </c>
       <c r="W12" t="n">
-        <v>-65.08734</v>
+        <v>-58.8161</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ronan Deposit</t>
+          <t>Ossokmanuan Lake South Quarry</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>012B/10/Ba 003</t>
+          <t>023H/06/Stn001</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Strontium, Barium</t>
+          <t>Gabbro</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1480,23 +1480,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>30</v>
       </c>
       <c r="V14" t="n">
-        <v>48.56074</v>
+        <v>53.40462</v>
       </c>
       <c r="W14" t="n">
-        <v>-58.8161</v>
+        <v>-65.08734</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F10%2FBa%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=023H%2F06%2FStn001</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lockport Mine</t>
+          <t>Lower Fischells Brook</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>002E/06/Cu 003</t>
+          <t>012B/07/Gyp003</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Zinc, Lead, Gold, Silver, Copper</t>
+          <t>Anhydrite, Gypsum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1624,23 +1624,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="U16" t="n">
         <v>30</v>
       </c>
       <c r="V16" t="n">
-        <v>49.45488</v>
+        <v>48.30663</v>
       </c>
       <c r="W16" t="n">
-        <v>-55.49811</v>
+        <v>-58.68165</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
         </is>
       </c>
     </row>
@@ -1650,24 +1650,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lower Fischells Brook</t>
+          <t>Lockport Mine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>012B/07/Gyp003</t>
+          <t>002E/06/Cu 003</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anhydrite, Gypsum</t>
+          <t>Zinc, Lead, Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1696,23 +1696,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T17" t="n">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="U17" t="n">
         <v>30</v>
       </c>
       <c r="V17" t="n">
-        <v>48.30663</v>
+        <v>49.45488</v>
       </c>
       <c r="W17" t="n">
-        <v>-58.68165</v>
+        <v>-55.49811</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012B%2F07%2FGyp003</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F06%2FCu%20003</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-O Zone</t>
+          <t>Daniel's Harbour Mine-P Zone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>012I/06/Zn 014</t>
+          <t>012I/06/Zn 015</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -1768,23 +1768,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="U18" t="n">
         <v>29</v>
       </c>
       <c r="V18" t="n">
-        <v>50.27283</v>
+        <v>50.31118</v>
       </c>
       <c r="W18" t="n">
-        <v>-57.46448</v>
+        <v>-57.43009</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daniel's Harbour Mine-P Zone</t>
+          <t>Daniel's Harbour Mine-O Zone</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>012I/06/Zn 015</t>
+          <t>012I/06/Zn 014</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -1840,23 +1840,23 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T19" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="U19" t="n">
         <v>29</v>
       </c>
       <c r="V19" t="n">
-        <v>50.31118</v>
+        <v>50.27283</v>
       </c>
       <c r="W19" t="n">
-        <v>-57.43009</v>
+        <v>-57.46448</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20015</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=012I%2F06%2FZn%20014</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cook Iron Mine</t>
+          <t>Workington</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>002E/11/Fe 001</t>
+          <t>002C/03/Fe 001</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Manganese</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Manganese, Iron</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>26</v>
       </c>
       <c r="V20" t="n">
-        <v>49.50376</v>
+        <v>48.00096</v>
       </c>
       <c r="W20" t="n">
-        <v>-55.21553</v>
+        <v>-53.01864</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
         </is>
       </c>
     </row>
@@ -2010,24 +2010,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Workington</t>
+          <t>Cook Iron Mine</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>002C/03/Fe 001</t>
+          <t>002E/11/Fe 001</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Manganese, Iron</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>26</v>
       </c>
       <c r="V22" t="n">
-        <v>48.00096</v>
+        <v>49.50376</v>
       </c>
       <c r="W22" t="n">
-        <v>-53.01864</v>
+        <v>-55.21553</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002C%2F03%2FFe%20001</t>
+          <t>https://gis.geosurv.gov.nl.ca/mods/ModsCard.asp?NMINOString=002E%2F11%2FFe%20001</t>
         </is>
       </c>
     </row>
